--- a/Jaipur-July-2025.xlsx
+++ b/Jaipur-July-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Jaipur</t>
   </si>
   <si>
@@ -115,7 +118,7 @@
     <t>HR55AX6981</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>ETIOS</t>
@@ -127,7 +130,7 @@
     <t>30/09/2019</t>
   </si>
   <si>
-    <t>-</t>
+    <t>30/09/2021</t>
   </si>
 </sst>
 </file>
@@ -489,10 +492,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,25 +574,28 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>261</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="2">
         <v>44471</v>
@@ -652,24 +658,24 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>262</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2">
         <v>44471</v>
@@ -732,27 +738,27 @@
         <v>64.25</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>263</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4">
         <v>101379</v>
@@ -812,27 +818,27 @@
         <v>65.13</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>264</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5">
         <v>237395</v>
@@ -892,24 +898,24 @@
         <v>55.06</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>265</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="2">
         <v>45997</v>
